--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y93"/>
+  <dimension ref="A1:Y74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.6.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 152â€¢TE</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L6: isolated marker/symbol line :: 1</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -650,7 +654,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L189: line starts with digit/letter garbage token | suspicious token(s): 1The (letter/digit mix) :: 1The free-for-all pace, which rumor</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •RIGHT•</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -708,19 +712,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L8: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Buyin â‚¬</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 152•TE</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L62: symbol-only separator/garbage line :: 348;</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -741,7 +745,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L471: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: ******* â€¢â€¢â€¢â€¢</t>
+          <t>L189: line starts with digit/letter garbage token | suspicious token(s): 1The (letter/digit mix) :: 1The free-for-all pace, which rumor</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -787,19 +791,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Kalamazoo, Mich.,Aug.â€” Feature-</t>
+          <t>L37: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: third and fourth ， between il. o. Me-</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢RIGHTâ€¢</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Buyin €</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: 5,</t>
+          <t>L8: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -814,13 +818,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John. ... 32</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John. ... 32</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L478: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----------0 F -</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -838,12 +842,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -862,19 +866,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Time â€” 2.08 Â½, 2.09 Â½.</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chicago, Aug. 4â€”The pace set By</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •RIGHT•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 3</t>
+          <t>L62: symbol-only separator/garbage line :: 348;</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -889,13 +893,13 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L439: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John ...618</t>
+          <t>L439: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John ...618</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L916: line starts with punctuation glued to text :: **THE HOUSE. OF GOOD CLOTHES"</t>
+          <t>L366: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton 27</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -937,19 +941,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Me for Hankâ€™s Pne Tree Circuit</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 0</t>
+          <t>L68: isolated marker/symbol line :: 5,</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -964,11 +968,15 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. Croix .. .586</t>
+          <t>L441: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. Croix .. .586</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton . .586</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1008,19 +1016,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Philadelphia, Aug. 4 â€” Accused of</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: -last week. Stafford, Fred Jamiesonâ€™s</t>
+          <t>L308: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ League Standing</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 1</t>
+          <t>L69: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1035,11 +1043,15 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 â€”</t>
+          <t>L446: punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 —</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L478: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----------0 F -</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1079,19 +1091,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L395: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Washingtonâ€”â€”â€”</t>
+          <t>L178: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Time-2.06% 2 ， 2.05 ， 2.07 ½.</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L334: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 0</t>
+          <t>L70: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1110,7 +1122,11 @@
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L916: line starts with punctuation glued to text :: **THE HOUSE. OF GOOD CLOTHES"</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1150,19 +1166,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L402: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Washington... 020010000 â€” 3104</t>
+          <t>L234: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L269: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Kalamazoo, Mich., -Aug.â€” Feature-</t>
+          <t>L335: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Pct. •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 6</t>
+          <t>L71: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1197,12 +1213,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1221,19 +1237,19 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L403: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Russell, Cicotte and</t>
+          <t>L424: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON :: Chicago:：：. 00100000-141</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ League Standing</t>
+          <t>L336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .604•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: Y</t>
+          <t>L72: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1273,7 +1289,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1287,24 +1303,24 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L808: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 02000030x (letter/digit mix) :: . .02000030xâ€”7 11 1</t>
+          <t>L808: suspicious token(s): 02000030x (letter/digit mix) :: . .02000030x—7 11 1</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Philadelphiaâ€”â€”</t>
+          <t>L453: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Philadelphia, Aug. 4â€”Accused of</t>
+          <t>L337: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L73: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1339,12 +1355,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1358,24 +1374,24 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
+          <t>L820: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150x—6 14 1</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L409: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Falkenberk,</t>
+          <t>L497: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L338: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 2</t>
+          <t>L74: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1429,24 +1445,24 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
+          <t>L872: punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223x—13 19 1</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At New York â€”</t>
+          <t>L649: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: $7.50, $ 8.00 ， $ 10.00 to $15.00</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Pct. â€¢</t>
+          <t>L339: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .265 •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1486,7 +1502,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1495,21 +1511,17 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L421: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Chicago â€”</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .604â€¢</t>
+          <t>L341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 3</t>
+          <t>L82: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1524,7 +1536,7 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Philadelphia. .. .000000402â€”6 10 3</t>
+          <t>L732: punctuation artifact: repeated periods :: Philadelphia. .. .000000402—6 10 3</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1558,36 +1570,32 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L429: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Pittsburghâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .563â€¢</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 2</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>L402: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Washington... 020010000 â€” 3104</t>
+          <t>L402: punctuation artifact: repeated periods :: Washington... 020010000 — 3104</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis.........021000000â€”3 7 0</t>
+          <t>L734: punctuation artifact: repeated periods :: St. Louis.........021000000—3 7 0</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1621,21 +1629,17 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L435: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Cincinnatiâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L338: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .563â€¢</t>
+          <t>L344: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 3</t>
+          <t>L84: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1650,7 +1654,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Chicago .........300200000â€”5 4</t>
+          <t>L744: punctuation artifact: repeated periods :: Chicago .........300200000—5 4</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1684,21 +1688,17 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At St. Louis â€”</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .265 â€¢</t>
+          <t>L345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Lose •</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 2</t>
+          <t>L95: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1735,26 +1735,22 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L453: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L346: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Two. •</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: A</t>
+          <t>L96: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L334: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -1786,26 +1782,22 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L463: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Coakley an</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L347: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .582•</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: O</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .604•</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -1837,26 +1829,22 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Montrealâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L348: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: F</t>
+          <t>L104: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L337: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1866,7 +1854,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Montreal ..........30300100201â€”7 10 3</t>
+          <t>L790: punctuation artifact: repeated periods :: Montreal ..........30300100201—7 10 3</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1888,26 +1876,22 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Providence... 10200120000 â€” 6 13</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Lose â€¢</t>
+          <t>L349: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: Â·</t>
+          <t>L107: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L338: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -1917,7 +1901,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L799: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Baltimore...........000111000â€”3 6 1</t>
+          <t>L799: punctuation artifact: repeated periods :: Baltimore...........000111000—3 6 1</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -1939,26 +1923,22 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Buffalo â€”</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Two. â€¢</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | symbol-only separator/garbage line :: .255 ♦</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 1</t>
+          <t>L109: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L339: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .265 •</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -1968,7 +1948,7 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Buffalo ............000000010â€”1 6 0</t>
+          <t>L801: punctuation artifact: repeated periods :: Buffalo ............000000010—1 6 0</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1990,26 +1970,22 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L491: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wilmington, Del., Aug. 4â€”Buck""</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L347: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .582â€¢</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L160: isolated marker/symbol line :: 1</t>
+          <t>L110: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L356: isolated marker/symbol line :: 21</t>
+          <t>L341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -2019,7 +1995,7 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Detroit..........002000002â€”4 15 3</t>
+          <t>L818: punctuation artifact: repeated periods :: Detroit..........002000002—4 15 3</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2044,19 +2020,19 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .540â€¢</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • • • •</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L162: isolated marker/symbol line :: 2</t>
+          <t>L112: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: 21</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -2066,7 +2042,7 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
+          <t>L820: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150x—6 14 1</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
@@ -2091,19 +2067,19 @@
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .540â€¢</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L164: isolated marker/symbol line :: 3</t>
+          <t>L159: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L358: symbol-only separator/garbage line :: 27 21</t>
+          <t>L344: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2138,19 +2114,19 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: .255 â™¦</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John. ... 32</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L166: symbol-only separator/garbage line :: 2.08</t>
+          <t>L160: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L360: isolated marker/symbol line :: 36</t>
+          <t>L347: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .582•</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -2160,7 +2136,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Brooklyn .........102000310â€”7 12</t>
+          <t>L853: punctuation artifact: repeated periods :: Brooklyn .........102000310—7 12</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2185,19 +2161,19 @@
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L366: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton 27</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L173: symbol-only separator/garbage line :: . 111</t>
+          <t>L162: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L410: isolated marker/symbol line :: Â°</t>
+          <t>L348: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -2207,7 +2183,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L862: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: New York.........000001100â€”2 7 0</t>
+          <t>L862: punctuation artifact: repeated periods :: New York.........000001100—2 7 0</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2232,19 +2208,19 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢ â€¢ â€¢</t>
+          <t>L406: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ St. Croix.</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L182: symbol-only separator/garbage line :: . 111</t>
+          <t>L164: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L349: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2254,7 +2230,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Pittsburg .......000000010â€”1 3 1</t>
+          <t>L864: punctuation artifact: repeated periods :: Pittsburg .......000000010—1 3 1</t>
         </is>
       </c>
       <c r="R28" s="1" t="inlineStr"/>
@@ -2279,19 +2255,19 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢1</t>
+          <t>L408: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Bangor.........13</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L187: isolated marker/symbol line :: .</t>
+          <t>L166: symbol-only separator/garbage line :: 2.08</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | symbol-only separator/garbage line :: .255 ♦</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr">
@@ -2301,7 +2277,7 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
+          <t>L872: punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223x—13 19 1</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2326,29 +2302,29 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John. ... 32</t>
+          <t>L411: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L188: isolated marker/symbol line :: .</t>
+          <t>L173: symbol-only separator/garbage line :: . 111</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Providence... 10200120000 â€” 6 13</t>
+          <t>L468: punctuation artifact: repeated periods :: Providence... 10200120000 — 6 13</t>
         </is>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston..........120000001â€” 4 7 1</t>
+          <t>L874: punctuation artifact: repeated periods :: Boston..........120000001— 4 7 1</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2373,19 +2349,19 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Fredericton 27</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L189: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 2 2 4</t>
+          <t>L182: symbol-only separator/garbage line :: . 111</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • • • •</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -2416,19 +2392,19 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>L384: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Charlie Oâ€™Brien, the St. John club's</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L193: symbol-only separator/garbage line :: . 333</t>
+          <t>L187: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L426: isolated marker/symbol line :: p</t>
+          <t>L356: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -2459,19 +2435,19 @@
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ St. Croix.</t>
+          <t>L414: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L188: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L427: isolated marker/symbol line :: I.</t>
+          <t>L357: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -2502,19 +2478,19 @@
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>L408: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ Bangor.........13</t>
+          <t>L439: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John ...618</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L287: symbol-only separator/garbage line :: . 317.</t>
+          <t>L189: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 2 2 4</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L431: symbol-only separator/garbage line :: .600</t>
+          <t>L358: symbol-only separator/garbage line :: 27 21</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2541,19 +2517,19 @@
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton . .586</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L341: isolated marker/symbol line :: n</t>
+          <t>L193: symbol-only separator/garbage line :: . 333</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L432: symbol-only separator/garbage line :: .560</t>
+          <t>L360: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2580,19 +2556,19 @@
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L441: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. Croix .. .586</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L345: isolated marker/symbol line :: 21</t>
+          <t>L234: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L433: symbol-only separator/garbage line :: .560</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2619,19 +2595,19 @@
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L442: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Bangor . . . .294</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L346: symbol-only separator/garbage line :: . 604</t>
+          <t>L287: symbol-only separator/garbage line :: . 317.</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L434: symbol-only separator/garbage line :: .275</t>
+          <t>L410: isolated marker/symbol line :: °</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2658,19 +2634,19 @@
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L471: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: ******* ••••</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L348: isolated marker/symbol line :: 21</t>
+          <t>L341: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L758: isolated marker/symbol line :: 1</t>
+          <t>L411: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2697,19 +2673,19 @@
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>L439: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John ...618</t>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L349: symbol-only separator/garbage line :: . 563</t>
+          <t>L345: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L759: isolated marker/symbol line :: 4</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2734,21 +2710,17 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L440: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Fredericton . .586</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: 21</t>
+          <t>L346: symbol-only separator/garbage line :: . 604</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L840: isolated marker/symbol line :: %</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2773,21 +2745,17 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. Croix .. .586</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L352: symbol-only separator/garbage line :: . 563</t>
+          <t>L348: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L414: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2812,21 +2780,17 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ Bangor . . . .294</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L354: isolated marker/symbol line :: 36</t>
+          <t>L349: symbol-only separator/garbage line :: . 563</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L844: symbol-only separator/garbage line | punctuation artifact: repeated exclamation marks :: 2/1/07!!!!!!!!!!!!!!</t>
+          <t>L426: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2851,21 +2815,17 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 â€”</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L355: symbol-only separator/garbage line :: . 265</t>
+          <t>L351: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L846: symbol-only separator/garbage line :: 20 22</t>
+          <t>L427: isolated marker/symbol line :: I.</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2890,21 +2850,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Timeâ€”2.06%2, 2.05%, 2.07%.</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L363: symbol-only separator/garbage line :: . 600</t>
+          <t>L352: symbol-only separator/garbage line :: . 563</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L881: isolated marker/symbol line :: a</t>
+          <t>L431: symbol-only separator/garbage line :: .600</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2929,21 +2885,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L471: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: ******* â€¢â€¢â€¢â€¢</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L364: symbol-only separator/garbage line :: . 582</t>
+          <t>L354: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L886: isolated marker/symbol line :: :</t>
+          <t>L432: symbol-only separator/garbage line :: .560</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2968,19 +2920,19 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”JUST A FEWâ€”</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L366: symbol-only separator/garbage line :: . 560</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L355: symbol-only separator/garbage line :: . 265</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L433: symbol-only separator/garbage line :: .560</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -3003,19 +2955,19 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Timeâ€”2.12, 2.08%, 1.07.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L367: symbol-only separator/garbage line :: . 540</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L363: symbol-only separator/garbage line :: . 600</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L434: symbol-only separator/garbage line :: .275</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3038,19 +2990,19 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wilmington, Del., Aug. 4â€”"Buck"</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L369: symbol-only separator/garbage line :: . . 586</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr"/>
+          <t>L364: symbol-only separator/garbage line :: . 582</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L471: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: ******* ••••</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3073,19 +3025,19 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Next Game at Scullyâ€™s</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L370: symbol-only separator/garbage line :: . 560</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr"/>
+          <t>L366: symbol-only separator/garbage line :: . 560</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>L758: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr"/>
       <c r="R49" s="1" t="inlineStr"/>
@@ -3108,19 +3060,19 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: oneâ€� yesterday. Lajoie, while at bat,</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L371: symbol-only separator/garbage line :: . 540</t>
-        </is>
-      </c>
-      <c r="O50" s="1" t="inlineStr"/>
+          <t>L367: symbol-only separator/garbage line :: . 540</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L759: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr"/>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3143,19 +3095,19 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L599: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Oâ€™Loughlin, and Sheridan was appeal-</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L373: symbol-only separator/garbage line :: . 275</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr"/>
+          <t>L369: symbol-only separator/garbage line :: . . 586</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>L806: symbol-only separator/garbage line :: .010000000—1 2 2</t>
+        </is>
+      </c>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr"/>
       <c r="R51" s="1" t="inlineStr"/>
@@ -3178,19 +3130,19 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L710: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Morey or PetÃ¨ Condon the other,</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L374: symbol-only separator/garbage line :: . 255</t>
-        </is>
-      </c>
-      <c r="O52" s="1" t="inlineStr"/>
+          <t>L370: symbol-only separator/garbage line :: . 560</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L840: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr"/>
       <c r="R52" s="1" t="inlineStr"/>
@@ -3213,19 +3165,19 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: at St. John to-morrow.â€”J. D. B.</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L391: isolated marker/symbol line :: E</t>
-        </is>
-      </c>
-      <c r="O53" s="1" t="inlineStr"/>
+          <t>L371: symbol-only separator/garbage line :: . 540</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
       <c r="R53" s="1" t="inlineStr"/>
@@ -3248,19 +3200,19 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L730: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At St Louisâ€”</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L392: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O54" s="1" t="inlineStr"/>
+          <t>L373: symbol-only separator/garbage line :: . 275</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>L844: symbol-only separator/garbage line | punctuation artifact: repeated exclamation marks :: 2/1/07!!!!!!!!!!!!!!</t>
+        </is>
+      </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr"/>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3283,19 +3235,19 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Philadelphia. .. .000000402â€”6 10 3</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L416: isolated marker/symbol line :: 3</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr"/>
+          <t>L374: symbol-only separator/garbage line :: . 255</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>L846: symbol-only separator/garbage line :: 20 22</t>
+        </is>
+      </c>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr"/>
       <c r="R55" s="1" t="inlineStr"/>
@@ -3318,19 +3270,19 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis.........021000000â€”3 7 0</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L423: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O56" s="1" t="inlineStr"/>
+          <t>L391: isolated marker/symbol line :: E</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>L881: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr"/>
       <c r="R56" s="1" t="inlineStr"/>
@@ -3353,19 +3305,19 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L742: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Washingtonâ€”</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L425: isolated marker/symbol line :: 4</t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="inlineStr"/>
+          <t>L392: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>L886: isolated marker/symbol line :: :</t>
+        </is>
+      </c>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
       <c r="R57" s="1" t="inlineStr"/>
@@ -3388,16 +3340,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Chicago .........300200000â€”5 4</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L426: isolated marker/symbol line :: 1</t>
+          <t>L416: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3423,16 +3371,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Washington. . . .020010000â€”3 10</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L451: isolated marker/symbol line :: 4</t>
+          <t>L423: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3458,16 +3402,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L748: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Russell. Cicotte and</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L453: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L425: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3493,16 +3433,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L768: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Torontoâ€”First game:</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L459: isolated marker/symbol line :: 4</t>
+          <t>L426: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3528,16 +3464,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Jersey. . . .00001000000001â€”2 13 1</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L461: isolated marker/symbol line :: 8</t>
+          <t>L451: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3563,16 +3495,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Toronto. . . .00000001000000â€”1 12 4</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L462: isolated marker/symbol line :: 0</t>
+          <t>L453: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3598,16 +3526,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Montrealâ€”</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L469: isolated marker/symbol line :: 3</t>
+          <t>L459: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3633,16 +3557,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L788: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Providence. . . .10200120000â€”6 13 3</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L471: isolated marker/symbol line :: 3</t>
+          <t>L461: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3668,16 +3588,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Montreal ..........30300100201â€”7 10 3</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L477: isolated marker/symbol line :: 6</t>
+          <t>L462: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3703,16 +3619,12 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L792: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 2 Batteriesâ€”Sline, Reisigi and Ons-</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L478: isolated marker/symbol line :: 1</t>
+          <t>L469: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3738,16 +3650,12 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L797: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Buffaloâ€”</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L480: isolated marker/symbol line :: 6</t>
+          <t>L471: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3773,16 +3681,12 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L799: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Baltimore...........000111000â€”3 6 1</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L481: isolated marker/symbol line :: 0</t>
+          <t>L477: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3808,16 +3712,12 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Buffalo ............000000010â€”1 6 0</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L657: isolated marker/symbol line :: R</t>
+          <t>L478: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3843,14 +3743,14 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Roth and Egan; Bebe,</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>L480: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
       <c r="O71" s="1" t="inlineStr"/>
       <c r="P71" s="1" t="inlineStr"/>
       <c r="Q71" s="1" t="inlineStr"/>
@@ -3874,14 +3774,14 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: .010000000â€”1 2 2</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
-      <c r="N72" s="1" t="inlineStr"/>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>L481: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O72" s="1" t="inlineStr"/>
       <c r="P72" s="1" t="inlineStr"/>
       <c r="Q72" s="1" t="inlineStr"/>
@@ -3905,14 +3805,14 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L808: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 02000030x (letter/digit mix) :: . .02000030xâ€”7 11 1</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>L497: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
       <c r="O73" s="1" t="inlineStr"/>
       <c r="P73" s="1" t="inlineStr"/>
       <c r="Q73" s="1" t="inlineStr"/>
@@ -3936,14 +3836,14 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Falkenberk, Kahler,</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
-      <c r="N74" s="1" t="inlineStr"/>
+      <c r="N74" s="1" t="inlineStr">
+        <is>
+          <t>L657: isolated marker/symbol line :: R</t>
+        </is>
+      </c>
       <c r="O74" s="1" t="inlineStr"/>
       <c r="P74" s="1" t="inlineStr"/>
       <c r="Q74" s="1" t="inlineStr"/>
@@ -3956,595 +3856,6 @@
       <c r="X74" s="1" t="inlineStr"/>
       <c r="Y74" s="1" t="inlineStr"/>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="1" t="inlineStr"/>
-      <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At New Yorkâ€”</t>
-        </is>
-      </c>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
-      <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" s="1" t="inlineStr"/>
-      <c r="Q75" s="1" t="inlineStr"/>
-      <c r="R75" s="1" t="inlineStr"/>
-      <c r="S75" s="1" t="inlineStr"/>
-      <c r="T75" s="1" t="inlineStr"/>
-      <c r="U75" s="1" t="inlineStr"/>
-      <c r="V75" s="1" t="inlineStr"/>
-      <c r="W75" s="1" t="inlineStr"/>
-      <c r="X75" s="1" t="inlineStr"/>
-      <c r="Y75" s="1" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr"/>
-      <c r="B76" s="1" t="inlineStr"/>
-      <c r="C76" s="1" t="inlineStr"/>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Detroit..........002000002â€”4 15 3</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" s="1" t="inlineStr"/>
-      <c r="Q76" s="1" t="inlineStr"/>
-      <c r="R76" s="1" t="inlineStr"/>
-      <c r="S76" s="1" t="inlineStr"/>
-      <c r="T76" s="1" t="inlineStr"/>
-      <c r="U76" s="1" t="inlineStr"/>
-      <c r="V76" s="1" t="inlineStr"/>
-      <c r="W76" s="1" t="inlineStr"/>
-      <c r="X76" s="1" t="inlineStr"/>
-      <c r="Y76" s="1" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr"/>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr"/>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
-      <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="inlineStr"/>
-      <c r="R77" s="1" t="inlineStr"/>
-      <c r="S77" s="1" t="inlineStr"/>
-      <c r="T77" s="1" t="inlineStr"/>
-      <c r="U77" s="1" t="inlineStr"/>
-      <c r="V77" s="1" t="inlineStr"/>
-      <c r="W77" s="1" t="inlineStr"/>
-      <c r="X77" s="1" t="inlineStr"/>
-      <c r="Y77" s="1" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr"/>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L822: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Willett, Dubue and Mc-</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
-      <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="inlineStr"/>
-      <c r="R78" s="1" t="inlineStr"/>
-      <c r="S78" s="1" t="inlineStr"/>
-      <c r="T78" s="1" t="inlineStr"/>
-      <c r="U78" s="1" t="inlineStr"/>
-      <c r="V78" s="1" t="inlineStr"/>
-      <c r="W78" s="1" t="inlineStr"/>
-      <c r="X78" s="1" t="inlineStr"/>
-      <c r="Y78" s="1" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr"/>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr"/>
-      <c r="R79" s="1" t="inlineStr"/>
-      <c r="S79" s="1" t="inlineStr"/>
-      <c r="T79" s="1" t="inlineStr"/>
-      <c r="U79" s="1" t="inlineStr"/>
-      <c r="V79" s="1" t="inlineStr"/>
-      <c r="W79" s="1" t="inlineStr"/>
-      <c r="X79" s="1" t="inlineStr"/>
-      <c r="Y79" s="1" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L851: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Chicagoâ€”</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr"/>
-      <c r="R80" s="1" t="inlineStr"/>
-      <c r="S80" s="1" t="inlineStr"/>
-      <c r="T80" s="1" t="inlineStr"/>
-      <c r="U80" s="1" t="inlineStr"/>
-      <c r="V80" s="1" t="inlineStr"/>
-      <c r="W80" s="1" t="inlineStr"/>
-      <c r="X80" s="1" t="inlineStr"/>
-      <c r="Y80" s="1" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr"/>
-      <c r="E81" s="1" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Brooklyn .........102000310â€”7 12</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr"/>
-      <c r="R81" s="1" t="inlineStr"/>
-      <c r="S81" s="1" t="inlineStr"/>
-      <c r="T81" s="1" t="inlineStr"/>
-      <c r="U81" s="1" t="inlineStr"/>
-      <c r="V81" s="1" t="inlineStr"/>
-      <c r="W81" s="1" t="inlineStr"/>
-      <c r="X81" s="1" t="inlineStr"/>
-      <c r="Y81" s="1" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L855: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chicago. . . . . .001000000â€”1 4</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
-      <c r="R82" s="1" t="inlineStr"/>
-      <c r="S82" s="1" t="inlineStr"/>
-      <c r="T82" s="1" t="inlineStr"/>
-      <c r="U82" s="1" t="inlineStr"/>
-      <c r="V82" s="1" t="inlineStr"/>
-      <c r="W82" s="1" t="inlineStr"/>
-      <c r="X82" s="1" t="inlineStr"/>
-      <c r="Y82" s="1" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L857: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Allen and Miller; Moore,</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
-      <c r="R83" s="1" t="inlineStr"/>
-      <c r="S83" s="1" t="inlineStr"/>
-      <c r="T83" s="1" t="inlineStr"/>
-      <c r="U83" s="1" t="inlineStr"/>
-      <c r="V83" s="1" t="inlineStr"/>
-      <c r="W83" s="1" t="inlineStr"/>
-      <c r="X83" s="1" t="inlineStr"/>
-      <c r="Y83" s="1" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L860: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Pittsburgâ€”</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr"/>
-      <c r="R84" s="1" t="inlineStr"/>
-      <c r="S84" s="1" t="inlineStr"/>
-      <c r="T84" s="1" t="inlineStr"/>
-      <c r="U84" s="1" t="inlineStr"/>
-      <c r="V84" s="1" t="inlineStr"/>
-      <c r="W84" s="1" t="inlineStr"/>
-      <c r="X84" s="1" t="inlineStr"/>
-      <c r="Y84" s="1" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L862: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: New York.........000001100â€”2 7 0</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
-      <c r="R85" s="1" t="inlineStr"/>
-      <c r="S85" s="1" t="inlineStr"/>
-      <c r="T85" s="1" t="inlineStr"/>
-      <c r="U85" s="1" t="inlineStr"/>
-      <c r="V85" s="1" t="inlineStr"/>
-      <c r="W85" s="1" t="inlineStr"/>
-      <c r="X85" s="1" t="inlineStr"/>
-      <c r="Y85" s="1" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Pittsburg .......000000010â€”1 3 1</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
-      <c r="R86" s="1" t="inlineStr"/>
-      <c r="S86" s="1" t="inlineStr"/>
-      <c r="T86" s="1" t="inlineStr"/>
-      <c r="U86" s="1" t="inlineStr"/>
-      <c r="V86" s="1" t="inlineStr"/>
-      <c r="W86" s="1" t="inlineStr"/>
-      <c r="X86" s="1" t="inlineStr"/>
-      <c r="Y86" s="1" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr"/>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Demaree, Marquard and</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="inlineStr"/>
-      <c r="S87" s="1" t="inlineStr"/>
-      <c r="T87" s="1" t="inlineStr"/>
-      <c r="U87" s="1" t="inlineStr"/>
-      <c r="V87" s="1" t="inlineStr"/>
-      <c r="W87" s="1" t="inlineStr"/>
-      <c r="X87" s="1" t="inlineStr"/>
-      <c r="Y87" s="1" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L870: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Cincinnatiâ€”</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
-      <c r="R88" s="1" t="inlineStr"/>
-      <c r="S88" s="1" t="inlineStr"/>
-      <c r="T88" s="1" t="inlineStr"/>
-      <c r="U88" s="1" t="inlineStr"/>
-      <c r="V88" s="1" t="inlineStr"/>
-      <c r="W88" s="1" t="inlineStr"/>
-      <c r="X88" s="1" t="inlineStr"/>
-      <c r="Y88" s="1" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
-      <c r="S89" s="1" t="inlineStr"/>
-      <c r="T89" s="1" t="inlineStr"/>
-      <c r="U89" s="1" t="inlineStr"/>
-      <c r="V89" s="1" t="inlineStr"/>
-      <c r="W89" s="1" t="inlineStr"/>
-      <c r="X89" s="1" t="inlineStr"/>
-      <c r="Y89" s="1" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr"/>
-      <c r="B90" s="1" t="inlineStr"/>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr"/>
-      <c r="E90" s="1" t="inlineStr"/>
-      <c r="F90" s="1" t="inlineStr"/>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston..........120000001â€” 4 7 1</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr"/>
-      <c r="R90" s="1" t="inlineStr"/>
-      <c r="S90" s="1" t="inlineStr"/>
-      <c r="T90" s="1" t="inlineStr"/>
-      <c r="U90" s="1" t="inlineStr"/>
-      <c r="V90" s="1" t="inlineStr"/>
-      <c r="W90" s="1" t="inlineStr"/>
-      <c r="X90" s="1" t="inlineStr"/>
-      <c r="Y90" s="1" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="1" t="inlineStr"/>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr"/>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Rudolph, Noyes</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr"/>
-      <c r="M91" s="1" t="inlineStr"/>
-      <c r="N91" s="1" t="inlineStr"/>
-      <c r="O91" s="1" t="inlineStr"/>
-      <c r="P91" s="1" t="inlineStr"/>
-      <c r="Q91" s="1" t="inlineStr"/>
-      <c r="R91" s="1" t="inlineStr"/>
-      <c r="S91" s="1" t="inlineStr"/>
-      <c r="T91" s="1" t="inlineStr"/>
-      <c r="U91" s="1" t="inlineStr"/>
-      <c r="V91" s="1" t="inlineStr"/>
-      <c r="W91" s="1" t="inlineStr"/>
-      <c r="X91" s="1" t="inlineStr"/>
-      <c r="Y91" s="1" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="1" t="inlineStr"/>
-      <c r="C92" s="1" t="inlineStr"/>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L894: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” , â€” the finest selected american leaf tobacco.</t>
-        </is>
-      </c>
-      <c r="L92" s="1" t="inlineStr"/>
-      <c r="M92" s="1" t="inlineStr"/>
-      <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr"/>
-      <c r="P92" s="1" t="inlineStr"/>
-      <c r="Q92" s="1" t="inlineStr"/>
-      <c r="R92" s="1" t="inlineStr"/>
-      <c r="S92" s="1" t="inlineStr"/>
-      <c r="T92" s="1" t="inlineStr"/>
-      <c r="U92" s="1" t="inlineStr"/>
-      <c r="V92" s="1" t="inlineStr"/>
-      <c r="W92" s="1" t="inlineStr"/>
-      <c r="X92" s="1" t="inlineStr"/>
-      <c r="Y92" s="1" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="1" t="inlineStr"/>
-      <c r="C93" s="1" t="inlineStr"/>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr"/>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L921: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 46.</t>
-        </is>
-      </c>
-      <c r="L93" s="1" t="inlineStr"/>
-      <c r="M93" s="1" t="inlineStr"/>
-      <c r="N93" s="1" t="inlineStr"/>
-      <c r="O93" s="1" t="inlineStr"/>
-      <c r="P93" s="1" t="inlineStr"/>
-      <c r="Q93" s="1" t="inlineStr"/>
-      <c r="R93" s="1" t="inlineStr"/>
-      <c r="S93" s="1" t="inlineStr"/>
-      <c r="T93" s="1" t="inlineStr"/>
-      <c r="U93" s="1" t="inlineStr"/>
-      <c r="V93" s="1" t="inlineStr"/>
-      <c r="W93" s="1" t="inlineStr"/>
-      <c r="X93" s="1" t="inlineStr"/>
-      <c r="Y93" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
